--- a/activities/02 - Map the Process and Spot the Waste/data/A02-Data-Workbook.xlsx
+++ b/activities/02 - Map the Process and Spot the Waste/data/A02-Data-Workbook.xlsx
@@ -515,7 +515,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Certified Lean Six Sigma White Belt (CLSSWB) Training  ·  TGS-2025053210  ·  Version v4</t>
+          <t>Certified Lean Six Sigma White Belt (CLSSWB) Training  ·  TGS-2025053210  ·  Version v5</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>60 customers observed end to end during one weekday morning rush at BrewBean Cafe. Wait time is measured from the customer joining the queue to the drink being handed over. This is THE baseline dataset for the course — Lab 3's Pareto is derived from the Delay Reason column and Lab 5's control chart compares back to it.</t>
+          <t>60 customers observed end to end during one weekday morning rush at BrewBean Cafe. Wait time is measured from the customer joining the queue to the drink being handed over. This is THE baseline dataset for the course — Activity 3's Pareto is derived from the Delay Reason column and Activity 5's control chart compares back to it.</t>
         </is>
       </c>
     </row>

--- a/activities/02 - Map the Process and Spot the Waste/data/A02-Data-Workbook.xlsx
+++ b/activities/02 - Map the Process and Spot the Waste/data/A02-Data-Workbook.xlsx
@@ -515,7 +515,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Certified Lean Six Sigma White Belt (CLSSWB) Training  ·  TGS-2025053210  ·  Version v5</t>
+          <t>Certified Lean Six Sigma White Belt (CLSSWB) Training  ·  TGS-2025053210  ·  Version v6</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>The average observed time for each step of the morning-rush process, with the team's value-add judgement left blank in the template. Use it for Step 3 and Step 4 of the lab.</t>
+          <t>The average observed time for each step of the morning-rush process, with the team's value-add judgement left blank in the template. Use it for Step 3 and Step 4 of the activity.</t>
         </is>
       </c>
     </row>

--- a/activities/02 - Map the Process and Spot the Waste/data/A02-Data-Workbook.xlsx
+++ b/activities/02 - Map the Process and Spot the Waste/data/A02-Data-Workbook.xlsx
@@ -515,7 +515,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Certified Lean Six Sigma White Belt (CLSSWB) Training  ·  TGS-2025053210  ·  Version v6</t>
+          <t>Certified Lean Six Sigma White Belt (CLSSWB) Training  ·  TGS-2025053210  ·  Version v7</t>
         </is>
       </c>
     </row>
